--- a/demo-StatsPAI-skill/tables/table2_main_ols.xlsx
+++ b/demo-StatsPAI-skill/tables/table2_main_ols.xlsx
@@ -53,7 +53,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -62,7 +62,30 @@
       <diagonal/>
     </border>
     <border>
-      <bottom style="medium"/>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -70,17 +93,23 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -449,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -466,149 +495,621 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>(1) Bivariate</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>(2) +Mincer</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>(3) +Demog.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>(4) +Region FE</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>(1) Bivariate</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>(2) +Mincer</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>(3) +Demog.</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>(4) +Region FE</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>5.571***</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>4.469***</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>4.734***</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>4.621***</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>(0.039)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>(0.070)</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>(0.070)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>(0.074)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Years of schooling</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>0.052***</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>0.093***</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>0.074***</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>0.075***</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>(0.003)</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>(0.004)</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>(0.004)</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>(0.004)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>exper</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0.090***</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>0.084***</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>0.085***</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>(0.007)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>(0.007)</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>(0.007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>expersq</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>-0.190***</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>-0.199***</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>(0.017)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>(0.018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>south</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>-0.125***</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>-0.148***</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>(0.015)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>(0.028)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>smsa</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>0.161***</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0.136***</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>(0.015)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>(0.019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>smsa66</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0.026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>(0.019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>reg662</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0.096***</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>(0.035)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>reg663</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>0.145***</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>(0.034)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>reg664</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>0.055</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>(0.041)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>reg665</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>0.128***</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>(0.043)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>reg666</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>0.141***</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr"/>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>(0.045)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>reg667</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>0.118***</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>(0.046)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>reg668</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>-0.056</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr"/>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>(0.051)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>reg669</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>0.119***</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr"/>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>(0.039)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>3,010</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>3,010</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>3,010</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>3,010</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>R²</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>0.099</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>0.196</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>0.291</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>0.300</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Standard errors in parentheses</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>* p&lt;0.10, ** p&lt;0.05, *** p&lt;0.01</t>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>*** p&lt;0.01, ** p&lt;0.05, * p&lt;0.10</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>